--- a/OUTPUT/reverse_A0A0B6P4W3_Yersinia_pestis_KIM10_.xlsx
+++ b/OUTPUT/reverse_A0A0B6P4W3_Yersinia_pestis_KIM10_.xlsx
@@ -482,11 +482,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.261</v>
+        <v>0.2610955617752899</v>
       </c>
     </row>
   </sheetData>
